--- a/public/import-templates/08_lesson_contents_template.xlsx
+++ b/public/import-templates/08_lesson_contents_template.xlsx
@@ -155,7 +155,7 @@
     <t>resource_type</t>
   </si>
   <si>
-    <t>video|pdf|link|image</t>
+    <t>video|pdf|link|mindmap|experiment</t>
   </si>
   <si>
     <t>url</t>
